--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU46"/>
+  <dimension ref="A1:AU47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>6.12</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5896,10 +5896,10 @@
         <v>0</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-11-03 19:30:00</t>
+          <t>2026-11-03 17:30:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-11-03 21:00:00</t>
+          <t>2026-11-03 19:30:00</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G39">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G45">
@@ -7760,156 +7760,319 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Hammam-Sousse</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Etoile du Sahel</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>0</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>0</v>
+      </c>
+      <c r="AG46">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
+        <v>0</v>
+      </c>
+      <c r="AK46">
+        <v>0</v>
+      </c>
+      <c r="AL46">
+        <v>0</v>
+      </c>
+      <c r="AM46">
+        <v>-1</v>
+      </c>
+      <c r="AN46">
+        <v>-1</v>
+      </c>
+      <c r="AO46">
+        <v>-1</v>
+      </c>
+      <c r="AP46">
+        <v>-1</v>
+      </c>
+      <c r="AQ46">
+        <v>0</v>
+      </c>
+      <c r="AR46">
+        <v>0</v>
+      </c>
+      <c r="AS46">
+        <v>0</v>
+      </c>
+      <c r="AT46">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>2026-11-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46" t="inlineStr">
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N46">
+      <c r="N47">
         <v>1.62</v>
       </c>
-      <c r="O46">
+      <c r="O47">
         <v>4.18</v>
       </c>
-      <c r="P46">
+      <c r="P47">
         <v>5.41</v>
       </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="T46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>0</v>
-      </c>
-      <c r="V46">
-        <v>0</v>
-      </c>
-      <c r="W46">
-        <v>0</v>
-      </c>
-      <c r="X46">
-        <v>0</v>
-      </c>
-      <c r="Y46">
-        <v>0</v>
-      </c>
-      <c r="Z46">
-        <v>0</v>
-      </c>
-      <c r="AA46">
-        <v>0</v>
-      </c>
-      <c r="AB46">
-        <v>0</v>
-      </c>
-      <c r="AC46">
-        <v>0</v>
-      </c>
-      <c r="AD46">
-        <v>0</v>
-      </c>
-      <c r="AE46">
-        <v>0</v>
-      </c>
-      <c r="AF46">
-        <v>0</v>
-      </c>
-      <c r="AG46">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>0</v>
-      </c>
-      <c r="AK46">
-        <v>0</v>
-      </c>
-      <c r="AL46">
-        <v>0</v>
-      </c>
-      <c r="AM46">
-        <v>-1</v>
-      </c>
-      <c r="AN46">
-        <v>-1</v>
-      </c>
-      <c r="AO46">
-        <v>-1</v>
-      </c>
-      <c r="AP46">
-        <v>-1</v>
-      </c>
-      <c r="AQ46">
-        <v>0</v>
-      </c>
-      <c r="AR46">
-        <v>0</v>
-      </c>
-      <c r="AS46">
-        <v>0</v>
-      </c>
-      <c r="AT46">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
         <is>
           <t>2026-11-03 21:30:00</t>
         </is>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G25">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.16</v>
+        <v>4.52</v>
       </c>
       <c r="O29">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
       <c r="P29">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB29">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>4.52</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>4.21</v>
+        <v>3.74</v>
       </c>
       <c r="P30">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>1.75</v>
       </c>
       <c r="AB30">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.67</v>
+        <v>4.16</v>
       </c>
       <c r="O31">
-        <v>4.37</v>
+        <v>4.27</v>
       </c>
       <c r="P31">
-        <v>5.29</v>
+        <v>1.85</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.16</v>
+        <v>1.32</v>
       </c>
       <c r="O32">
-        <v>3.89</v>
+        <v>6.12</v>
       </c>
       <c r="P32">
-        <v>3.39</v>
+        <v>10.6</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,16 +5564,16 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="O33">
-        <v>3.74</v>
+        <v>3.89</v>
       </c>
       <c r="P33">
-        <v>3.19</v>
+        <v>3.39</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="O34">
-        <v>6.12</v>
+        <v>4.37</v>
       </c>
       <c r="P34">
-        <v>10.6</v>
+        <v>5.29</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,16 +5890,16 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G36">

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>4.52</v>
+        <v>2.3</v>
       </c>
       <c r="O29">
-        <v>4.21</v>
+        <v>3.74</v>
       </c>
       <c r="P29">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5078,7 +5078,7 @@
         <v>1.75</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>4.16</v>
       </c>
       <c r="O30">
-        <v>3.74</v>
+        <v>4.27</v>
       </c>
       <c r="P30">
-        <v>3.19</v>
+        <v>1.85</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>4.16</v>
+        <v>2.16</v>
       </c>
       <c r="O31">
-        <v>4.27</v>
+        <v>3.89</v>
       </c>
       <c r="P31">
-        <v>1.85</v>
+        <v>3.39</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="O32">
-        <v>6.12</v>
+        <v>4.37</v>
       </c>
       <c r="P32">
-        <v>10.6</v>
+        <v>5.29</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,16 +5564,16 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.16</v>
+        <v>1.32</v>
       </c>
       <c r="O33">
-        <v>3.89</v>
+        <v>6.12</v>
       </c>
       <c r="P33">
-        <v>3.39</v>
+        <v>10.6</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,16 +5727,16 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.67</v>
+        <v>4.52</v>
       </c>
       <c r="O34">
-        <v>4.37</v>
+        <v>4.21</v>
       </c>
       <c r="P34">
-        <v>5.29</v>
+        <v>1.8</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB34">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>4.16</v>
+        <v>2.16</v>
       </c>
       <c r="O30">
-        <v>4.27</v>
+        <v>3.89</v>
       </c>
       <c r="P30">
-        <v>1.85</v>
+        <v>3.39</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="O31">
-        <v>3.89</v>
+        <v>4.37</v>
       </c>
       <c r="P31">
-        <v>3.39</v>
+        <v>5.29</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="O32">
-        <v>4.37</v>
+        <v>6.12</v>
       </c>
       <c r="P32">
-        <v>5.29</v>
+        <v>10.6</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,16 +5564,16 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.32</v>
+        <v>4.52</v>
       </c>
       <c r="O33">
-        <v>6.12</v>
+        <v>4.21</v>
       </c>
       <c r="P33">
-        <v>10.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,16 +5727,16 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.52</v>
+        <v>4.16</v>
       </c>
       <c r="O34">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="P34">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G25">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.52</v>
+        <v>2.16</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="P28">
-        <v>2.14</v>
+        <v>3.39</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB28">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="O29">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>3.19</v>
+        <v>2.14</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB29">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="P30">
-        <v>3.39</v>
+        <v>3.19</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G36">

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.16</v>
+        <v>1.32</v>
       </c>
       <c r="O28">
-        <v>3.89</v>
+        <v>6.12</v>
       </c>
       <c r="P28">
-        <v>3.39</v>
+        <v>10.6</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4912,16 +4912,16 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.52</v>
+        <v>2.16</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="P29">
-        <v>2.14</v>
+        <v>3.39</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB29">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="O30">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>3.19</v>
+        <v>2.14</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="O31">
-        <v>4.37</v>
+        <v>3.74</v>
       </c>
       <c r="P31">
-        <v>5.29</v>
+        <v>3.19</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="O32">
-        <v>6.12</v>
+        <v>4.37</v>
       </c>
       <c r="P32">
-        <v>10.6</v>
+        <v>5.29</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,16 +5564,16 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE32">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G25">
@@ -6349,55 +6349,55 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G46">

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU47"/>
+  <dimension ref="A1:AU49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G12">
@@ -2261,68 +2261,68 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-11-03 10:30:00</t>
+          <t>2026-11-03 09:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,68 +2424,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="O13">
+        <v>2.55</v>
+      </c>
+      <c r="P13">
+        <v>2.8</v>
+      </c>
+      <c r="Q13">
+        <v>3.4</v>
+      </c>
+      <c r="R13">
+        <v>1.65</v>
+      </c>
+      <c r="S13">
+        <v>1.67</v>
+      </c>
+      <c r="T13">
+        <v>1.94</v>
+      </c>
+      <c r="U13">
+        <v>4</v>
+      </c>
+      <c r="V13">
+        <v>1.17</v>
+      </c>
+      <c r="W13">
+        <v>1.02</v>
+      </c>
+      <c r="X13">
+        <v>1.14</v>
+      </c>
+      <c r="Y13">
+        <v>1.7</v>
+      </c>
+      <c r="Z13">
+        <v>1.78</v>
+      </c>
+      <c r="AA13">
         <v>3.14</v>
       </c>
-      <c r="P13">
-        <v>2.32</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-11-03 14:00:00</t>
+          <t>2026-11-03 10:30:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-11-03 14:00:00</t>
+          <t>2026-11-03 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.22</v>
+        <v>2.81</v>
       </c>
       <c r="O15">
-        <v>3.86</v>
+        <v>3.14</v>
       </c>
       <c r="P15">
-        <v>3.27</v>
+        <v>2.32</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-11-03 14:45:00</t>
+          <t>2026-11-03 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="O16">
-        <v>4.01</v>
+        <v>3.28</v>
       </c>
       <c r="P16">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AB16">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-11-03 14:45:00</t>
+          <t>2026-11-03 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-11-03 15:00:00</t>
+          <t>2026-11-03 14:45:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.65</v>
+        <v>3.72</v>
       </c>
       <c r="O18">
-        <v>3.1</v>
+        <v>4.01</v>
       </c>
       <c r="P18">
-        <v>2.59</v>
+        <v>2.01</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z18">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AC18">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE18">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK18">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-11-03 16:45:00</t>
+          <t>2026-11-03 14:45:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-11-03 16:45:00</t>
+          <t>2026-11-03 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G26">
@@ -4543,68 +4543,68 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N26">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,68 +4869,68 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N28">
-        <v>1.32</v>
+        <v>2.32</v>
       </c>
       <c r="O28">
-        <v>6.12</v>
+        <v>3.45</v>
       </c>
       <c r="P28">
-        <v>10.6</v>
+        <v>2.88</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC28">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="AD28">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-11-03 17:00:00</t>
+          <t>2026-11-03 16:45:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="O29">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="P29">
-        <v>3.39</v>
+        <v>3.9</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-11-03 17:00:00</t>
+          <t>2026-11-03 16:45:00</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.52</v>
+        <v>1.32</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>6.12</v>
       </c>
       <c r="P30">
-        <v>2.14</v>
+        <v>10.6</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,16 +5238,16 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="O31">
-        <v>3.74</v>
+        <v>3.89</v>
       </c>
       <c r="P31">
-        <v>3.19</v>
+        <v>3.39</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.67</v>
+        <v>3.52</v>
       </c>
       <c r="O32">
-        <v>4.37</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>5.29</v>
+        <v>2.14</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.52</v>
+        <v>2.3</v>
       </c>
       <c r="O33">
-        <v>4.21</v>
+        <v>3.74</v>
       </c>
       <c r="P33">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5730,7 +5730,7 @@
         <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.16</v>
+        <v>1.67</v>
       </c>
       <c r="O34">
-        <v>4.27</v>
+        <v>4.37</v>
       </c>
       <c r="P34">
-        <v>1.85</v>
+        <v>5.29</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-11-03 17:30:00</t>
+          <t>2026-11-03 17:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-11-03 19:30:00</t>
+          <t>2026-11-03 17:00:00</t>
         </is>
       </c>
     </row>
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-11-03 21:00:00</t>
+          <t>2026-11-03 17:30:00</t>
         </is>
       </c>
     </row>
@@ -6782,27 +6782,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-11-03 21:00:00</t>
+          <t>2026-11-03 19:30:00</t>
         </is>
       </c>
     </row>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G46">
@@ -7923,156 +7923,482 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Hammam-Sousse</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Etoile du Sahel</t>
+        </is>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>0</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>0</v>
+      </c>
+      <c r="AG47">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>0</v>
+      </c>
+      <c r="AK47">
+        <v>0</v>
+      </c>
+      <c r="AL47">
+        <v>0</v>
+      </c>
+      <c r="AM47">
+        <v>-1</v>
+      </c>
+      <c r="AN47">
+        <v>-1</v>
+      </c>
+      <c r="AO47">
+        <v>-1</v>
+      </c>
+      <c r="AP47">
+        <v>-1</v>
+      </c>
+      <c r="AQ47">
+        <v>0</v>
+      </c>
+      <c r="AR47">
+        <v>0</v>
+      </c>
+      <c r="AS47">
+        <v>0</v>
+      </c>
+      <c r="AT47">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>2026-11-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tunisia Ligue 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Club Africain</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jeunesse Sportive Omrane</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
+        <v>0</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0</v>
+      </c>
+      <c r="AG48">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>0</v>
+      </c>
+      <c r="AK48">
+        <v>0</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>-1</v>
+      </c>
+      <c r="AN48">
+        <v>-1</v>
+      </c>
+      <c r="AO48">
+        <v>-1</v>
+      </c>
+      <c r="AP48">
+        <v>-1</v>
+      </c>
+      <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
+        <v>0</v>
+      </c>
+      <c r="AS48">
+        <v>0</v>
+      </c>
+      <c r="AT48">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>2026-11-03 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Coritiba</t>
         </is>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47" t="inlineStr">
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N47">
+      <c r="N49">
         <v>1.62</v>
       </c>
-      <c r="O47">
+      <c r="O49">
         <v>4.18</v>
       </c>
-      <c r="P47">
+      <c r="P49">
         <v>5.41</v>
       </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="T47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>0</v>
-      </c>
-      <c r="V47">
-        <v>0</v>
-      </c>
-      <c r="W47">
-        <v>0</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
-      </c>
-      <c r="Y47">
-        <v>0</v>
-      </c>
-      <c r="Z47">
-        <v>0</v>
-      </c>
-      <c r="AA47">
-        <v>0</v>
-      </c>
-      <c r="AB47">
-        <v>0</v>
-      </c>
-      <c r="AC47">
-        <v>0</v>
-      </c>
-      <c r="AD47">
-        <v>0</v>
-      </c>
-      <c r="AE47">
-        <v>0</v>
-      </c>
-      <c r="AF47">
-        <v>0</v>
-      </c>
-      <c r="AG47">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>0</v>
-      </c>
-      <c r="AK47">
-        <v>0</v>
-      </c>
-      <c r="AL47">
-        <v>0</v>
-      </c>
-      <c r="AM47">
-        <v>-1</v>
-      </c>
-      <c r="AN47">
-        <v>-1</v>
-      </c>
-      <c r="AO47">
-        <v>-1</v>
-      </c>
-      <c r="AP47">
-        <v>-1</v>
-      </c>
-      <c r="AQ47">
-        <v>0</v>
-      </c>
-      <c r="AR47">
-        <v>0</v>
-      </c>
-      <c r="AS47">
-        <v>0</v>
-      </c>
-      <c r="AT47">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
+        <v>0</v>
+      </c>
+      <c r="AF49">
+        <v>0</v>
+      </c>
+      <c r="AG49">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>0</v>
+      </c>
+      <c r="AK49">
+        <v>0</v>
+      </c>
+      <c r="AL49">
+        <v>0</v>
+      </c>
+      <c r="AM49">
+        <v>-1</v>
+      </c>
+      <c r="AN49">
+        <v>-1</v>
+      </c>
+      <c r="AO49">
+        <v>-1</v>
+      </c>
+      <c r="AP49">
+        <v>-1</v>
+      </c>
+      <c r="AQ49">
+        <v>0</v>
+      </c>
+      <c r="AR49">
+        <v>0</v>
+      </c>
+      <c r="AS49">
+        <v>0</v>
+      </c>
+      <c r="AT49">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
         <is>
           <t>2026-11-03 21:30:00</t>
         </is>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G27">

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.32</v>
+        <v>2.16</v>
       </c>
       <c r="O30">
-        <v>6.12</v>
+        <v>3.89</v>
       </c>
       <c r="P30">
-        <v>10.6</v>
+        <v>3.39</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,16 +5238,16 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.16</v>
+        <v>3.52</v>
       </c>
       <c r="O31">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>3.39</v>
+        <v>2.14</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.52</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="P32">
-        <v>2.14</v>
+        <v>3.19</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="O33">
-        <v>3.74</v>
+        <v>4.37</v>
       </c>
       <c r="P33">
-        <v>3.19</v>
+        <v>5.29</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.67</v>
+        <v>4.52</v>
       </c>
       <c r="O34">
-        <v>4.37</v>
+        <v>4.21</v>
       </c>
       <c r="P34">
-        <v>5.29</v>
+        <v>1.8</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB34">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>4.52</v>
+        <v>4.16</v>
       </c>
       <c r="O35">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="P35">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB35">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.16</v>
+        <v>1.32</v>
       </c>
       <c r="O36">
-        <v>4.27</v>
+        <v>6.12</v>
       </c>
       <c r="P36">
-        <v>1.85</v>
+        <v>10.6</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,16 +6216,16 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE36">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC39">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G4">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC26">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>3.89</v>
+        <v>3.74</v>
       </c>
       <c r="P30">
-        <v>3.39</v>
+        <v>3.19</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.52</v>
+        <v>2.16</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="P31">
-        <v>2.14</v>
+        <v>3.39</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="O32">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>3.19</v>
+        <v>2.14</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB32">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC38">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.21</v>
+        <v>2.25</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB23">
         <v>2.15</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.25</v>
+        <v>3.21</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P25">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB25">
         <v>2.15</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.16</v>
+        <v>4.52</v>
       </c>
       <c r="O31">
-        <v>3.89</v>
+        <v>4.21</v>
       </c>
       <c r="P31">
-        <v>3.39</v>
+        <v>1.8</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.52</v>
+        <v>2.16</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="P32">
-        <v>2.14</v>
+        <v>3.39</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.67</v>
+        <v>3.52</v>
       </c>
       <c r="O33">
-        <v>4.37</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>5.29</v>
+        <v>2.14</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB33">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.52</v>
+        <v>1.67</v>
       </c>
       <c r="O34">
-        <v>4.21</v>
+        <v>4.37</v>
       </c>
       <c r="P34">
-        <v>1.8</v>
+        <v>5.29</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>9.35</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3451,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE19">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G9">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.81</v>
+        <v>3.28</v>
       </c>
       <c r="O15">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="P15">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.28</v>
+        <v>2.81</v>
       </c>
       <c r="O16">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="P16">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AA16">
         <v>1.85</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,34 +3089,34 @@
         <v>3.27</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA17">
         <v>1.55</v>
@@ -3125,19 +3125,19 @@
         <v>2.3</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,34 +3252,34 @@
         <v>2.01</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA18">
         <v>1.6</v>
@@ -3288,19 +3288,19 @@
         <v>2.2</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,40 +3415,40 @@
         <v>9.35</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC19">
         <v>1.9</v>
@@ -3457,13 +3457,13 @@
         <v>1.8</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3741,34 +3741,34 @@
         <v>2.9</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA21">
         <v>1.9</v>
@@ -3777,19 +3777,19 @@
         <v>1.78</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,34 +3904,34 @@
         <v>3</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
         <v>1.8</v>
@@ -3940,19 +3940,19 @@
         <v>1.88</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4067,34 +4067,34 @@
         <v>2.88</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA23">
         <v>1.6</v>
@@ -4103,19 +4103,19 @@
         <v>2.15</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="O25">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA25">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB25">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.6</v>
+        <v>3.21</v>
       </c>
       <c r="O26">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P26">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA26">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AB26">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>3.07</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA27">
         <v>1.8</v>
@@ -4755,19 +4755,19 @@
         <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G28">
@@ -4869,84 +4869,84 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N28">
-        <v>2.32</v>
+        <v>1.84</v>
       </c>
       <c r="O28">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="P28">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="Q28">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="V28">
+        <v>1.6</v>
+      </c>
+      <c r="W28">
+        <v>1.13</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>1.1</v>
+      </c>
+      <c r="Z28">
+        <v>5.2</v>
+      </c>
+      <c r="AA28">
         <v>1.44</v>
       </c>
-      <c r="W28">
-        <v>1.11</v>
-      </c>
-      <c r="X28">
-        <v>1.04</v>
-      </c>
-      <c r="Y28">
+      <c r="AB28">
+        <v>2.43</v>
+      </c>
+      <c r="AC28">
+        <v>2.22</v>
+      </c>
+      <c r="AD28">
+        <v>1.62</v>
+      </c>
+      <c r="AE28">
         <v>1.21</v>
       </c>
-      <c r="Z28">
-        <v>4.33</v>
-      </c>
-      <c r="AA28">
+      <c r="AF28">
+        <v>1.42</v>
+      </c>
+      <c r="AG28">
+        <v>2.61</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>1.2</v>
+      </c>
+      <c r="AK28">
         <v>1.73</v>
-      </c>
-      <c r="AB28">
-        <v>2.03</v>
-      </c>
-      <c r="AC28">
-        <v>2.8</v>
-      </c>
-      <c r="AD28">
-        <v>1.42</v>
-      </c>
-      <c r="AE28">
-        <v>1.1</v>
-      </c>
-      <c r="AF28">
-        <v>1.57</v>
-      </c>
-      <c r="AG28">
-        <v>2.25</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.28</v>
-      </c>
-      <c r="AK28">
-        <v>1.57</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G29">
@@ -5032,68 +5032,68 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.84</v>
+        <v>2.32</v>
       </c>
       <c r="O29">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="P29">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,34 +5208,34 @@
         <v>3.19</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA30">
         <v>1.75</v>
@@ -5244,19 +5244,19 @@
         <v>1.98</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5371,34 +5371,34 @@
         <v>1.8</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA31">
         <v>1.75</v>
@@ -5407,19 +5407,19 @@
         <v>1.95</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,34 +5534,34 @@
         <v>3.39</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA32">
         <v>1.6</v>
@@ -5570,19 +5570,19 @@
         <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,34 +5697,34 @@
         <v>2.14</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="AA33">
         <v>1.66</v>
@@ -5733,19 +5733,19 @@
         <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,34 +5860,34 @@
         <v>5.29</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA34">
         <v>1.6</v>
@@ -5896,19 +5896,19 @@
         <v>2.2</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,34 +6023,34 @@
         <v>1.85</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA35">
         <v>1.66</v>
@@ -6059,19 +6059,19 @@
         <v>2.1</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,40 +6186,40 @@
         <v>10.6</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AC36">
         <v>1.98</v>
@@ -6228,13 +6228,13 @@
         <v>1.75</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="O37">
         <v>3.75</v>
       </c>
       <c r="P37">
+        <v>3.5</v>
+      </c>
+      <c r="Q37">
         <v>2.5</v>
       </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA37">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AB37">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="O38">
         <v>3.75</v>
       </c>
       <c r="P38">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AB38">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6675,34 +6675,34 @@
         <v>5.5</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA39">
         <v>1.97</v>
@@ -6711,19 +6711,19 @@
         <v>1.79</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hammam-Lif</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Hammam-Lif</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G47">

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G9">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,65 +3080,65 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.22</v>
+        <v>3.72</v>
       </c>
       <c r="O17">
-        <v>3.86</v>
+        <v>4.01</v>
       </c>
       <c r="P17">
-        <v>3.27</v>
+        <v>2.01</v>
       </c>
       <c r="Q17">
-        <v>2.49</v>
+        <v>3.43</v>
       </c>
       <c r="R17">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T17">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="U17">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA17">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
+        <v>2.2</v>
+      </c>
+      <c r="AC17">
+        <v>2.56</v>
+      </c>
+      <c r="AD17">
+        <v>1.5</v>
+      </c>
+      <c r="AE17">
+        <v>1.17</v>
+      </c>
+      <c r="AF17">
+        <v>1.56</v>
+      </c>
+      <c r="AG17">
         <v>2.3</v>
       </c>
-      <c r="AC17">
-        <v>2.08</v>
-      </c>
-      <c r="AD17">
-        <v>1.78</v>
-      </c>
-      <c r="AE17">
-        <v>1.3</v>
-      </c>
-      <c r="AF17">
-        <v>1.36</v>
-      </c>
-      <c r="AG17">
-        <v>2.93</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AK17">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.72</v>
+        <v>2.22</v>
       </c>
       <c r="O18">
-        <v>4.01</v>
+        <v>3.86</v>
       </c>
       <c r="P18">
-        <v>2.01</v>
+        <v>3.27</v>
       </c>
       <c r="Q18">
-        <v>3.43</v>
+        <v>2.49</v>
       </c>
       <c r="R18">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="U18">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z18">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB18">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC18">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="AD18">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AE18">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AF18">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AG18">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="Q23">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T23">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA23">
+        <v>1.83</v>
+      </c>
+      <c r="AB23">
+        <v>1.85</v>
+      </c>
+      <c r="AC23">
+        <v>2.78</v>
+      </c>
+      <c r="AD23">
+        <v>1.34</v>
+      </c>
+      <c r="AE23">
+        <v>1.1</v>
+      </c>
+      <c r="AF23">
         <v>1.6</v>
       </c>
-      <c r="AB23">
-        <v>2.15</v>
-      </c>
-      <c r="AC23">
-        <v>2.46</v>
-      </c>
-      <c r="AD23">
-        <v>1.43</v>
-      </c>
-      <c r="AE23">
-        <v>1.14</v>
-      </c>
-      <c r="AF23">
-        <v>1.53</v>
-      </c>
       <c r="AG23">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="Q24">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="R24">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="U24">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V24">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA24">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AC24">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="AD24">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>2.3</v>
+        <v>3.07</v>
       </c>
       <c r="Q25">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="U25">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V25">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W25">
         <v>1.08</v>
@@ -4417,31 +4417,31 @@
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z25">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="AA25">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AC25">
-        <v>2.59</v>
+        <v>2.83</v>
       </c>
       <c r="AD25">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE25">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AG25">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.21</v>
+        <v>2.8</v>
       </c>
       <c r="O26">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="R26">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T26">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="V26">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="W26">
+        <v>1.08</v>
+      </c>
+      <c r="X26">
+        <v>1.02</v>
+      </c>
+      <c r="Y26">
+        <v>1.17</v>
+      </c>
+      <c r="Z26">
+        <v>4</v>
+      </c>
+      <c r="AA26">
+        <v>1.68</v>
+      </c>
+      <c r="AB26">
+        <v>2.11</v>
+      </c>
+      <c r="AC26">
+        <v>2.59</v>
+      </c>
+      <c r="AD26">
+        <v>1.39</v>
+      </c>
+      <c r="AE26">
         <v>1.12</v>
       </c>
-      <c r="X26">
-        <v>1.01</v>
-      </c>
-      <c r="Y26">
-        <v>1.15</v>
-      </c>
-      <c r="Z26">
-        <v>4.2</v>
-      </c>
-      <c r="AA26">
-        <v>1.62</v>
-      </c>
-      <c r="AB26">
-        <v>2.15</v>
-      </c>
-      <c r="AC26">
-        <v>2.41</v>
-      </c>
-      <c r="AD26">
-        <v>1.45</v>
-      </c>
-      <c r="AE26">
-        <v>1.16</v>
-      </c>
       <c r="AF26">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG26">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AK26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
+        <v>3.21</v>
+      </c>
+      <c r="O27">
+        <v>3.55</v>
+      </c>
+      <c r="P27">
+        <v>2.08</v>
+      </c>
+      <c r="Q27">
+        <v>3.62</v>
+      </c>
+      <c r="R27">
+        <v>2.27</v>
+      </c>
+      <c r="S27">
+        <v>1.26</v>
+      </c>
+      <c r="T27">
+        <v>3.4</v>
+      </c>
+      <c r="U27">
         <v>2.23</v>
       </c>
-      <c r="O27">
-        <v>3.35</v>
-      </c>
-      <c r="P27">
-        <v>3.07</v>
-      </c>
-      <c r="Q27">
-        <v>2.75</v>
-      </c>
-      <c r="R27">
-        <v>2.16</v>
-      </c>
-      <c r="S27">
-        <v>1.3</v>
-      </c>
-      <c r="T27">
-        <v>3.14</v>
-      </c>
-      <c r="U27">
-        <v>2.45</v>
-      </c>
       <c r="V27">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA27">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC27">
-        <v>2.83</v>
+        <v>2.41</v>
       </c>
       <c r="AD27">
+        <v>1.45</v>
+      </c>
+      <c r="AE27">
+        <v>1.16</v>
+      </c>
+      <c r="AF27">
+        <v>1.52</v>
+      </c>
+      <c r="AG27">
+        <v>2.33</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.26</v>
+      </c>
+      <c r="AK27">
         <v>1.33</v>
-      </c>
-      <c r="AE27">
-        <v>1.09</v>
-      </c>
-      <c r="AF27">
-        <v>1.61</v>
-      </c>
-      <c r="AG27">
-        <v>2.15</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.28</v>
-      </c>
-      <c r="AK27">
-        <v>1.63</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>4.52</v>
+        <v>4.16</v>
       </c>
       <c r="O31">
-        <v>4.21</v>
+        <v>4.27</v>
       </c>
       <c r="P31">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q31">
-        <v>3.62</v>
+        <v>4.6</v>
       </c>
       <c r="R31">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="S31">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T31">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U31">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="V31">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="W31">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X31">
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z31">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA31">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB31">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AD31">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AE31">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AF31">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG31">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
         <v>1.2</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.16</v>
+        <v>3.52</v>
       </c>
       <c r="O32">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>3.39</v>
+        <v>2.14</v>
       </c>
       <c r="Q32">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="U32">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V32">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="W32">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z32">
-        <v>5.4</v>
+        <v>6.23</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AD32">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AE32">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AF32">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AG32">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,34 +5688,34 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.52</v>
+        <v>4.52</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>4.21</v>
       </c>
       <c r="P33">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="S33">
         <v>1.22</v>
       </c>
       <c r="T33">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V33">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W33">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -5724,28 +5724,28 @@
         <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>6.23</v>
+        <v>6.5</v>
       </c>
       <c r="AA33">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD33">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE33">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF33">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AG33">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
+        <v>1.18</v>
+      </c>
+      <c r="AK33">
         <v>1.2</v>
-      </c>
-      <c r="AK33">
-        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>4.16</v>
+        <v>2.16</v>
       </c>
       <c r="O35">
-        <v>4.27</v>
+        <v>3.89</v>
       </c>
       <c r="P35">
-        <v>1.85</v>
+        <v>3.39</v>
       </c>
       <c r="Q35">
-        <v>4.6</v>
+        <v>2.3</v>
       </c>
       <c r="R35">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="S35">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="U35">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="V35">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="W35">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X35">
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AA35">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB35">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC35">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
       <c r="AD35">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AE35">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="AF35">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG35">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6838,55 +6838,55 @@
         <v>2.26</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G43">
@@ -8305,55 +8305,55 @@
         <v>5.41</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G8">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.3</v>
+        <v>4.16</v>
       </c>
       <c r="O30">
-        <v>3.74</v>
+        <v>4.27</v>
       </c>
       <c r="P30">
-        <v>3.19</v>
+        <v>1.85</v>
       </c>
       <c r="Q30">
-        <v>2.71</v>
+        <v>4.6</v>
       </c>
       <c r="R30">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S30">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="U30">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="V30">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="W30">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X30">
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z30">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="AA30">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
-        <v>2.23</v>
+        <v>1.96</v>
       </c>
       <c r="AD30">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AE30">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AF30">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG30">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK30">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>4.16</v>
+        <v>2.3</v>
       </c>
       <c r="O31">
-        <v>4.27</v>
+        <v>3.74</v>
       </c>
       <c r="P31">
-        <v>1.85</v>
+        <v>3.19</v>
       </c>
       <c r="Q31">
-        <v>4.6</v>
+        <v>2.71</v>
       </c>
       <c r="R31">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="U31">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="V31">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X31">
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AA31">
+        <v>1.75</v>
+      </c>
+      <c r="AB31">
+        <v>1.98</v>
+      </c>
+      <c r="AC31">
+        <v>2.23</v>
+      </c>
+      <c r="AD31">
         <v>1.66</v>
       </c>
-      <c r="AB31">
-        <v>2.1</v>
-      </c>
-      <c r="AC31">
-        <v>1.96</v>
-      </c>
-      <c r="AD31">
-        <v>1.88</v>
-      </c>
       <c r="AE31">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AF31">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG31">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK31">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Progrès Sakiet Eddaïer</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Progrès Sakiet Eddaïer</t>
         </is>
       </c>
       <c r="G45">

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,65 +4221,65 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="P24">
-        <v>2.88</v>
+        <v>3.07</v>
       </c>
       <c r="Q24">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="U24">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V24">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z24">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="AA24">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AB24">
+        <v>1.9</v>
+      </c>
+      <c r="AC24">
+        <v>2.83</v>
+      </c>
+      <c r="AD24">
+        <v>1.33</v>
+      </c>
+      <c r="AE24">
+        <v>1.09</v>
+      </c>
+      <c r="AF24">
+        <v>1.61</v>
+      </c>
+      <c r="AG24">
         <v>2.15</v>
       </c>
-      <c r="AC24">
-        <v>2.46</v>
-      </c>
-      <c r="AD24">
-        <v>1.43</v>
-      </c>
-      <c r="AE24">
-        <v>1.14</v>
-      </c>
-      <c r="AF24">
-        <v>1.53</v>
-      </c>
-      <c r="AG24">
-        <v>2.31</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R25">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="U25">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V25">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z25">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA25">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AC25">
-        <v>2.83</v>
+        <v>2.46</v>
       </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE25">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF25">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK25">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.52</v>
+        <v>1.67</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>4.37</v>
       </c>
       <c r="P32">
+        <v>5.29</v>
+      </c>
+      <c r="Q32">
+        <v>1.85</v>
+      </c>
+      <c r="R32">
+        <v>2.6</v>
+      </c>
+      <c r="S32">
+        <v>1.24</v>
+      </c>
+      <c r="T32">
+        <v>3.55</v>
+      </c>
+      <c r="U32">
         <v>2.14</v>
       </c>
-      <c r="Q32">
-        <v>3.1</v>
-      </c>
-      <c r="R32">
-        <v>2.38</v>
-      </c>
-      <c r="S32">
-        <v>1.22</v>
-      </c>
-      <c r="T32">
-        <v>4.33</v>
-      </c>
-      <c r="U32">
-        <v>2.08</v>
-      </c>
       <c r="V32">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W32">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>6.23</v>
+        <v>6.5</v>
       </c>
       <c r="AA32">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AD32">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AE32">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AF32">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AG32">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK32">
-        <v>1.28</v>
+        <v>2.79</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,34 +5688,34 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.52</v>
+        <v>3.52</v>
       </c>
       <c r="O33">
-        <v>4.21</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="Q33">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
         <v>1.22</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U33">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V33">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W33">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -5724,28 +5724,28 @@
         <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>6.5</v>
+        <v>6.23</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB33">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD33">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE33">
+        <v>1.34</v>
+      </c>
+      <c r="AF33">
         <v>1.33</v>
       </c>
-      <c r="AF33">
-        <v>1.43</v>
-      </c>
       <c r="AG33">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.67</v>
+        <v>4.52</v>
       </c>
       <c r="O34">
-        <v>4.37</v>
+        <v>4.21</v>
       </c>
       <c r="P34">
-        <v>5.29</v>
+        <v>1.8</v>
       </c>
       <c r="Q34">
-        <v>1.85</v>
+        <v>3.62</v>
       </c>
       <c r="R34">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="S34">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V34">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W34">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X34">
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z34">
         <v>6.5</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB34">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AD34">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE34">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AG34">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>2.79</v>
+        <v>1.2</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -4903,7 +4903,7 @@
         <v>1.13</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
         <v>1.1</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,34 +5688,34 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.52</v>
+        <v>4.52</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>4.21</v>
       </c>
       <c r="P33">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="S33">
         <v>1.22</v>
       </c>
       <c r="T33">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V33">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W33">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -5724,28 +5724,28 @@
         <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>6.23</v>
+        <v>6.5</v>
       </c>
       <c r="AA33">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB33">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC33">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD33">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE33">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF33">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AG33">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
+        <v>1.18</v>
+      </c>
+      <c r="AK33">
         <v>1.2</v>
-      </c>
-      <c r="AK33">
-        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,34 +5851,34 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.52</v>
+        <v>3.52</v>
       </c>
       <c r="O34">
-        <v>4.21</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="Q34">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="R34">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
         <v>1.22</v>
       </c>
       <c r="T34">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U34">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V34">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W34">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -5887,28 +5887,28 @@
         <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>6.5</v>
+        <v>6.23</v>
       </c>
       <c r="AA34">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC34">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD34">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE34">
+        <v>1.34</v>
+      </c>
+      <c r="AF34">
         <v>1.33</v>
       </c>
-      <c r="AF34">
-        <v>1.43</v>
-      </c>
       <c r="AG34">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK34">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -2437,55 +2437,55 @@
         <v>2.8</v>
       </c>
       <c r="Q13">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R13">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S13">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="T13">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="U13">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="V13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W13">
         <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y13">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="Z13">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AA13">
-        <v>3.14</v>
+        <v>3.75</v>
       </c>
       <c r="AB13">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC13">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD13">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="AG13">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.28</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,34 +5688,34 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.52</v>
+        <v>3.52</v>
       </c>
       <c r="O33">
-        <v>4.21</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="Q33">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
         <v>1.22</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U33">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V33">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W33">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -5724,28 +5724,28 @@
         <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>6.5</v>
+        <v>6.23</v>
       </c>
       <c r="AA33">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB33">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC33">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD33">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE33">
+        <v>1.34</v>
+      </c>
+      <c r="AF33">
         <v>1.33</v>
       </c>
-      <c r="AF33">
-        <v>1.43</v>
-      </c>
       <c r="AG33">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,34 +5851,34 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.52</v>
+        <v>4.52</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>4.21</v>
       </c>
       <c r="P34">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="S34">
         <v>1.22</v>
       </c>
       <c r="T34">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V34">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W34">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -5887,28 +5887,28 @@
         <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>6.23</v>
+        <v>6.5</v>
       </c>
       <c r="AA34">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB34">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AC34">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD34">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE34">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF34">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AG34">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
+        <v>1.18</v>
+      </c>
+      <c r="AK34">
         <v>1.2</v>
-      </c>
-      <c r="AK34">
-        <v>1.28</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.28</v>
+        <v>3.97</v>
       </c>
       <c r="O15">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="P15">
-        <v>2.02</v>
+        <v>1.74</v>
       </c>
       <c r="Q15">
-        <v>4.75</v>
+        <v>4.81</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T15">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="U15">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W15">
         <v>1.07</v>
@@ -2787,19 +2787,19 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z15">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="AA15">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC15">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="AD15">
         <v>1.3</v>
@@ -2811,7 +2811,7 @@
         <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
         <v>1.2</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.81</v>
+        <v>2.67</v>
       </c>
       <c r="O16">
         <v>3.14</v>
       </c>
       <c r="P16">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="Q16">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="R16">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S16">
         <v>1.35</v>
@@ -2938,7 +2938,7 @@
         <v>3</v>
       </c>
       <c r="U16">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V16">
         <v>1.4</v>
@@ -2950,22 +2950,22 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z16">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="AA16">
         <v>1.85</v>
       </c>
       <c r="AB16">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC16">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
       <c r="AD16">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE16">
         <v>1.11</v>
@@ -2974,7 +2974,7 @@
         <v>1.65</v>
       </c>
       <c r="AG16">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
         <v>1.4</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O19">
-        <v>5.9</v>
+        <v>5.25</v>
       </c>
       <c r="P19">
-        <v>9.35</v>
+        <v>7.75</v>
       </c>
       <c r="Q19">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R19">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="S19">
         <v>1.22</v>
@@ -3427,13 +3427,13 @@
         <v>3.9</v>
       </c>
       <c r="U19">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="V19">
         <v>1.7</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3445,25 +3445,25 @@
         <v>5.75</v>
       </c>
       <c r="AA19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AC19">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AD19">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AE19">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.07</v>
       </c>
       <c r="AK19">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.65</v>
+        <v>2.84</v>
       </c>
       <c r="O20">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P20">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R20">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.35</v>
+      </c>
+      <c r="Z20">
+        <v>2.74</v>
+      </c>
+      <c r="AA20">
+        <v>2.2</v>
+      </c>
+      <c r="AB20">
+        <v>1.62</v>
+      </c>
+      <c r="AC20">
+        <v>3.9</v>
+      </c>
+      <c r="AD20">
+        <v>1.18</v>
+      </c>
+      <c r="AE20">
         <v>1.02</v>
       </c>
-      <c r="Y20">
-        <v>1.28</v>
-      </c>
-      <c r="Z20">
-        <v>3.08</v>
-      </c>
-      <c r="AA20">
-        <v>2</v>
-      </c>
-      <c r="AB20">
-        <v>1.8</v>
-      </c>
-      <c r="AC20">
-        <v>3.42</v>
-      </c>
-      <c r="AD20">
-        <v>1.23</v>
-      </c>
-      <c r="AE20">
-        <v>1.05</v>
-      </c>
       <c r="AF20">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG20">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.32</v>
       </c>
       <c r="AK20">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
         <v>2.9</v>
@@ -3771,10 +3771,10 @@
         <v>3.2</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB21">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC21">
         <v>3.2</v>
@@ -3789,7 +3789,7 @@
         <v>1.71</v>
       </c>
       <c r="AG21">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O22">
         <v>3.5</v>
       </c>
       <c r="P22">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q22">
         <v>2.8</v>
@@ -3910,10 +3910,10 @@
         <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U22">
         <v>2.6</v>
@@ -3934,10 +3934,10 @@
         <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB22">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC22">
         <v>3.04</v>
@@ -3952,7 +3952,7 @@
         <v>1.65</v>
       </c>
       <c r="AG22">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
         <v>2.6</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -4076,16 +4076,16 @@
         <v>1.31</v>
       </c>
       <c r="T23">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U23">
         <v>2.45</v>
       </c>
       <c r="V23">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1</v>
@@ -4097,10 +4097,10 @@
         <v>3.7</v>
       </c>
       <c r="AA23">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC23">
         <v>2.78</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="O24">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="R24">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="U24">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V24">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA24">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AB24">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AC24">
-        <v>2.83</v>
+        <v>2.46</v>
       </c>
       <c r="AD24">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE24">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Q25">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S25">
+        <v>1.3</v>
+      </c>
+      <c r="T25">
+        <v>3.14</v>
+      </c>
+      <c r="U25">
+        <v>2.45</v>
+      </c>
+      <c r="V25">
+        <v>1.47</v>
+      </c>
+      <c r="W25">
+        <v>1.08</v>
+      </c>
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>1.19</v>
+      </c>
+      <c r="Z25">
+        <v>3.78</v>
+      </c>
+      <c r="AA25">
+        <v>1.76</v>
+      </c>
+      <c r="AB25">
+        <v>1.99</v>
+      </c>
+      <c r="AC25">
+        <v>2.83</v>
+      </c>
+      <c r="AD25">
+        <v>1.33</v>
+      </c>
+      <c r="AE25">
+        <v>1.09</v>
+      </c>
+      <c r="AF25">
+        <v>1.61</v>
+      </c>
+      <c r="AG25">
+        <v>2.18</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.25</v>
       </c>
-      <c r="T25">
-        <v>3.6</v>
-      </c>
-      <c r="U25">
-        <v>2.4</v>
-      </c>
-      <c r="V25">
-        <v>1.5</v>
-      </c>
-      <c r="W25">
-        <v>1.11</v>
-      </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.16</v>
-      </c>
-      <c r="Z25">
-        <v>4.1</v>
-      </c>
-      <c r="AA25">
-        <v>1.6</v>
-      </c>
-      <c r="AB25">
-        <v>2.15</v>
-      </c>
-      <c r="AC25">
-        <v>2.46</v>
-      </c>
-      <c r="AD25">
-        <v>1.43</v>
-      </c>
-      <c r="AE25">
-        <v>1.14</v>
-      </c>
-      <c r="AF25">
-        <v>1.53</v>
-      </c>
-      <c r="AG25">
-        <v>2.31</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.26</v>
-      </c>
       <c r="AK25">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,25 +4556,25 @@
         <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T26">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U26">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="V26">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1.02</v>
@@ -4604,7 +4604,7 @@
         <v>1.55</v>
       </c>
       <c r="AG26">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,22 +4710,22 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q27">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="R27">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
         <v>3.4</v>
@@ -4734,7 +4734,7 @@
         <v>2.23</v>
       </c>
       <c r="V27">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W27">
         <v>1.12</v>
@@ -4749,10 +4749,10 @@
         <v>4.2</v>
       </c>
       <c r="AA27">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB27">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AC27">
         <v>2.41</v>
@@ -4767,7 +4767,7 @@
         <v>1.52</v>
       </c>
       <c r="AG27">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4876,31 +4876,31 @@
         <v>1.84</v>
       </c>
       <c r="O28">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="P28">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="R28">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="S28">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U28">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V28">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="W28">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4930,7 +4930,7 @@
         <v>1.42</v>
       </c>
       <c r="AG28">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
         <v>1.73</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="O29">
         <v>3.45</v>
       </c>
       <c r="P29">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q29">
         <v>2.88</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
         <v>3.5</v>
@@ -6352,13 +6352,13 @@
         <v>2.5</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U37">
         <v>2.55</v>
@@ -6379,10 +6379,10 @@
         <v>3.82</v>
       </c>
       <c r="AA37">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB37">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC37">
         <v>2.81</v>
@@ -6397,7 +6397,7 @@
         <v>1.63</v>
       </c>
       <c r="AG37">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O38">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q38">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -2769,28 +2769,28 @@
         <v>2.31</v>
       </c>
       <c r="S15">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
         <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA15">
         <v>1.84</v>
@@ -2802,7 +2802,7 @@
         <v>3.05</v>
       </c>
       <c r="AD15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE15">
         <v>1.08</v>
@@ -2811,7 +2811,7 @@
         <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>2.1</v>
       </c>
       <c r="S16">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
         <v>3</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q24">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S24">
+        <v>1.3</v>
+      </c>
+      <c r="T24">
+        <v>3.14</v>
+      </c>
+      <c r="U24">
+        <v>2.45</v>
+      </c>
+      <c r="V24">
+        <v>1.47</v>
+      </c>
+      <c r="W24">
+        <v>1.08</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.19</v>
+      </c>
+      <c r="Z24">
+        <v>3.78</v>
+      </c>
+      <c r="AA24">
+        <v>1.76</v>
+      </c>
+      <c r="AB24">
+        <v>1.99</v>
+      </c>
+      <c r="AC24">
+        <v>2.83</v>
+      </c>
+      <c r="AD24">
+        <v>1.33</v>
+      </c>
+      <c r="AE24">
+        <v>1.09</v>
+      </c>
+      <c r="AF24">
+        <v>1.61</v>
+      </c>
+      <c r="AG24">
+        <v>2.18</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.25</v>
       </c>
-      <c r="T24">
-        <v>3.32</v>
-      </c>
-      <c r="U24">
-        <v>2.4</v>
-      </c>
-      <c r="V24">
-        <v>1.5</v>
-      </c>
-      <c r="W24">
-        <v>1.11</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.16</v>
-      </c>
-      <c r="Z24">
-        <v>4.1</v>
-      </c>
-      <c r="AA24">
-        <v>1.64</v>
-      </c>
-      <c r="AB24">
-        <v>2.17</v>
-      </c>
-      <c r="AC24">
-        <v>2.46</v>
-      </c>
-      <c r="AD24">
-        <v>1.43</v>
-      </c>
-      <c r="AE24">
-        <v>1.14</v>
-      </c>
-      <c r="AF24">
-        <v>1.53</v>
-      </c>
-      <c r="AG24">
-        <v>2.35</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.26</v>
-      </c>
       <c r="AK24">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="R25">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T25">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="U25">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V25">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z25">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA25">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AB25">
-        <v>1.99</v>
+        <v>2.17</v>
       </c>
       <c r="AC25">
-        <v>2.83</v>
+        <v>2.46</v>
       </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE25">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF25">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG25">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK25">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -3080,22 +3080,22 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="O17">
-        <v>4.01</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
         <v>3.43</v>
       </c>
       <c r="R17">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
         <v>3</v>
@@ -3119,10 +3119,10 @@
         <v>4.1</v>
       </c>
       <c r="AA17">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AB17">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC17">
         <v>2.56</v>
@@ -3131,7 +3131,7 @@
         <v>1.5</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
         <v>1.56</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O18">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>3.27</v>
+        <v>2.82</v>
       </c>
       <c r="Q18">
         <v>2.49</v>
@@ -3282,10 +3282,10 @@
         <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AC18">
         <v>2.08</v>
@@ -3294,7 +3294,7 @@
         <v>1.78</v>
       </c>
       <c r="AE18">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF18">
         <v>1.36</v>
@@ -3316,7 +3316,7 @@
         <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O19">
         <v>5.25</v>
@@ -3445,7 +3445,7 @@
         <v>5.75</v>
       </c>
       <c r="AA19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB19">
         <v>2.56</v>
@@ -4064,7 +4064,7 @@
         <v>3.3</v>
       </c>
       <c r="P23">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Q23">
         <v>3.1</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q24">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="R24">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="U24">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V24">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z24">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA24">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AB24">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="AC24">
-        <v>2.83</v>
+        <v>2.46</v>
       </c>
       <c r="AD24">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE24">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AG24">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK24">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q25">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S25">
+        <v>1.3</v>
+      </c>
+      <c r="T25">
+        <v>3.14</v>
+      </c>
+      <c r="U25">
+        <v>2.45</v>
+      </c>
+      <c r="V25">
+        <v>1.47</v>
+      </c>
+      <c r="W25">
+        <v>1.08</v>
+      </c>
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>1.19</v>
+      </c>
+      <c r="Z25">
+        <v>3.78</v>
+      </c>
+      <c r="AA25">
+        <v>1.76</v>
+      </c>
+      <c r="AB25">
+        <v>1.99</v>
+      </c>
+      <c r="AC25">
+        <v>2.83</v>
+      </c>
+      <c r="AD25">
+        <v>1.33</v>
+      </c>
+      <c r="AE25">
+        <v>1.09</v>
+      </c>
+      <c r="AF25">
+        <v>1.61</v>
+      </c>
+      <c r="AG25">
+        <v>2.18</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.25</v>
       </c>
-      <c r="T25">
-        <v>3.32</v>
-      </c>
-      <c r="U25">
-        <v>2.4</v>
-      </c>
-      <c r="V25">
-        <v>1.5</v>
-      </c>
-      <c r="W25">
-        <v>1.11</v>
-      </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.16</v>
-      </c>
-      <c r="Z25">
-        <v>4.1</v>
-      </c>
-      <c r="AA25">
-        <v>1.64</v>
-      </c>
-      <c r="AB25">
-        <v>2.17</v>
-      </c>
-      <c r="AC25">
-        <v>2.46</v>
-      </c>
-      <c r="AD25">
-        <v>1.43</v>
-      </c>
-      <c r="AE25">
-        <v>1.14</v>
-      </c>
-      <c r="AF25">
-        <v>1.53</v>
-      </c>
-      <c r="AG25">
-        <v>2.35</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.26</v>
-      </c>
       <c r="AK25">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         <v>3.75</v>
       </c>
       <c r="P27">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q27">
         <v>3.5</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>4.16</v>
+        <v>2.3</v>
       </c>
       <c r="O30">
-        <v>4.27</v>
+        <v>3.75</v>
       </c>
       <c r="P30">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q30">
-        <v>4.6</v>
+        <v>2.71</v>
       </c>
       <c r="R30">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T30">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="V30">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="W30">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X30">
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AA30">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="AB30">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AC30">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AD30">
-        <v>1.88</v>
+        <v>1.59</v>
       </c>
       <c r="AE30">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AF30">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,34 +5362,34 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="O31">
-        <v>3.74</v>
+        <v>4.8</v>
       </c>
       <c r="P31">
-        <v>3.19</v>
+        <v>6</v>
       </c>
       <c r="Q31">
-        <v>2.71</v>
+        <v>1.85</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S31">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T31">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="U31">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="W31">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X31">
         <v>1</v>
@@ -5398,28 +5398,28 @@
         <v>1.13</v>
       </c>
       <c r="Z31">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA31">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="AB31">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="AC31">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AD31">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AE31">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF31">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG31">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AK31">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.67</v>
+        <v>2.91</v>
       </c>
       <c r="O32">
-        <v>4.37</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>5.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q32">
-        <v>1.85</v>
+        <v>3.6</v>
       </c>
       <c r="R32">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="U32">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V32">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="W32">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z32">
-        <v>6.5</v>
+        <v>6.23</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AC32">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD32">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AE32">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AF32">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AG32">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.09</v>
+        <v>1.75</v>
       </c>
       <c r="AK32">
-        <v>2.79</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,34 +5688,34 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.52</v>
+        <v>4.34</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="P33">
-        <v>2.14</v>
+        <v>1.67</v>
       </c>
       <c r="Q33">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="S33">
         <v>1.22</v>
       </c>
       <c r="T33">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U33">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V33">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W33">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -5724,28 +5724,28 @@
         <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>6.23</v>
+        <v>6.5</v>
       </c>
       <c r="AA33">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AB33">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AC33">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD33">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE33">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF33">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AG33">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
+        <v>1.18</v>
+      </c>
+      <c r="AK33">
         <v>1.2</v>
-      </c>
-      <c r="AK33">
-        <v>1.28</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.52</v>
+        <v>4.6</v>
       </c>
       <c r="O34">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="P34">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="Q34">
-        <v>3.62</v>
+        <v>4.6</v>
       </c>
       <c r="R34">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T34">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="U34">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="V34">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="W34">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X34">
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z34">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA34">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AB34">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="AC34">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="AD34">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AE34">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AF34">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK34">
         <v>1.2</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="O35">
-        <v>3.89</v>
+        <v>3.92</v>
       </c>
       <c r="P35">
-        <v>3.39</v>
+        <v>3.86</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -6041,7 +6041,7 @@
         <v>1.61</v>
       </c>
       <c r="W35">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X35">
         <v>1</v>
@@ -6053,16 +6053,16 @@
         <v>5.4</v>
       </c>
       <c r="AA35">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB35">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AC35">
         <v>2.31</v>
       </c>
       <c r="AD35">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AE35">
         <v>1.27</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O36">
-        <v>6.12</v>
+        <v>6.5</v>
       </c>
       <c r="P36">
-        <v>10.6</v>
+        <v>9</v>
       </c>
       <c r="Q36">
         <v>1.49</v>
@@ -6192,7 +6192,7 @@
         <v>3.1</v>
       </c>
       <c r="S36">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="T36">
         <v>5.75</v>
@@ -6213,28 +6213,28 @@
         <v>1.03</v>
       </c>
       <c r="Z36">
-        <v>9.85</v>
+        <v>9.5</v>
       </c>
       <c r="AA36">
         <v>1.22</v>
       </c>
       <c r="AB36">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="AC36">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AD36">
-        <v>1.75</v>
+        <v>2.41</v>
       </c>
       <c r="AE36">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF36">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG36">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6349,10 +6349,10 @@
         <v>3.5</v>
       </c>
       <c r="Q37">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
         <v>1.28</v>
@@ -6394,10 +6394,10 @@
         <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,34 +6512,34 @@
         <v>2.6</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA38">
         <v>1.58</v>
@@ -6548,19 +6548,19 @@
         <v>2.2</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="Q39">
         <v>2.16</v>
@@ -6690,10 +6690,10 @@
         <v>2.85</v>
       </c>
       <c r="V39">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W39">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
         <v>1.01</v>
@@ -6705,10 +6705,10 @@
         <v>3.11</v>
       </c>
       <c r="AA39">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB39">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AC39">
         <v>3.41</v>
@@ -6829,58 +6829,58 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O40">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="P40">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q40">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="R40">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T40">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U40">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V40">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z40">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AA40">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AB40">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AC40">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD40">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF40">
         <v>1.65</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AL40">
         <v>0</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -3445,7 +3445,7 @@
         <v>5.75</v>
       </c>
       <c r="AA19">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB19">
         <v>2.56</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O21">
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O27">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
         <v>2.1</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.91</v>
+        <v>4.6</v>
       </c>
       <c r="O32">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P32">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="Q32">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S32">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T32">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U32">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="V32">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="W32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z32">
-        <v>6.23</v>
+        <v>7.5</v>
       </c>
       <c r="AA32">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB32">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AC32">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AD32">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AE32">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF32">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AK32">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>4.6</v>
+        <v>2.91</v>
       </c>
       <c r="O34">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P34">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="Q34">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="R34">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="U34">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="V34">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="W34">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X34">
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>7.5</v>
+        <v>6.23</v>
       </c>
       <c r="AA34">
+        <v>1.4</v>
+      </c>
+      <c r="AB34">
+        <v>3</v>
+      </c>
+      <c r="AC34">
+        <v>2.05</v>
+      </c>
+      <c r="AD34">
+        <v>1.81</v>
+      </c>
+      <c r="AE34">
+        <v>1.35</v>
+      </c>
+      <c r="AF34">
         <v>1.36</v>
       </c>
-      <c r="AB34">
-        <v>3.2</v>
-      </c>
-      <c r="AC34">
-        <v>1.86</v>
-      </c>
-      <c r="AD34">
-        <v>1.88</v>
-      </c>
-      <c r="AE34">
-        <v>1.39</v>
-      </c>
-      <c r="AF34">
-        <v>1.44</v>
-      </c>
       <c r="AG34">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AK34">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>4.7</v>
       </c>
       <c r="AA38">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AB38">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC38">
         <v>2.33</v>
@@ -6832,7 +6832,7 @@
         <v>3.25</v>
       </c>
       <c r="O40">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P40">
         <v>2.1</v>
@@ -6871,7 +6871,7 @@
         <v>1.72</v>
       </c>
       <c r="AB40">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AC40">
         <v>2.75</v>
@@ -8296,16 +8296,16 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="O49">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="P49">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
       <c r="Q49">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="R49">
         <v>2.25</v>
@@ -8320,7 +8320,7 @@
         <v>2.6</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
         <v>1.11</v>
@@ -8332,22 +8332,22 @@
         <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AA49">
         <v>1.8</v>
       </c>
       <c r="AB49">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC49">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="AD49">
         <v>1.38</v>
       </c>
       <c r="AE49">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
         <v>1.8</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK49">
         <v>2.33</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -2827,7 +2827,7 @@
         <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3415,7 +3415,7 @@
         <v>7.75</v>
       </c>
       <c r="Q19">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R19">
         <v>2.7</v>
@@ -3433,7 +3433,7 @@
         <v>1.7</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3448,13 +3448,13 @@
         <v>1.47</v>
       </c>
       <c r="AB19">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AC19">
         <v>2.11</v>
       </c>
       <c r="AD19">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE19">
         <v>1.24</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O21">
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q21">
         <v>2.88</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,34 +5688,34 @@
         </is>
       </c>
       <c r="N33">
-        <v>4.34</v>
+        <v>2.91</v>
       </c>
       <c r="O33">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="P33">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="Q33">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="R33">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
         <v>1.22</v>
       </c>
       <c r="T33">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U33">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V33">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W33">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X33">
         <v>1</v>
@@ -5724,7 +5724,7 @@
         <v>1.1</v>
       </c>
       <c r="Z33">
-        <v>6.5</v>
+        <v>6.23</v>
       </c>
       <c r="AA33">
         <v>1.4</v>
@@ -5733,19 +5733,19 @@
         <v>3</v>
       </c>
       <c r="AC33">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD33">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE33">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF33">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AG33">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AK33">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,34 +5851,34 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.91</v>
+        <v>4.34</v>
       </c>
       <c r="O34">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="P34">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="Q34">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="S34">
         <v>1.22</v>
       </c>
       <c r="T34">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U34">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V34">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W34">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -5887,7 +5887,7 @@
         <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>6.23</v>
+        <v>6.5</v>
       </c>
       <c r="AA34">
         <v>1.4</v>
@@ -5896,19 +5896,19 @@
         <v>3</v>
       </c>
       <c r="AC34">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AD34">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF34">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AG34">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AK34">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q37">
-        <v>2.58</v>
+        <v>2.95</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S37">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="U37">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="V37">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z37">
-        <v>3.82</v>
+        <v>4.7</v>
       </c>
       <c r="AA37">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AB37">
-        <v>2.01</v>
+        <v>2.33</v>
       </c>
       <c r="AC37">
-        <v>2.81</v>
+        <v>2.33</v>
       </c>
       <c r="AD37">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE37">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF37">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AG37">
-        <v>2.13</v>
+        <v>2.53</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK37">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O38">
         <v>3.7</v>
       </c>
       <c r="P38">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q38">
-        <v>2.95</v>
+        <v>2.58</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T38">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="U38">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="V38">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z38">
-        <v>4.7</v>
+        <v>3.82</v>
       </c>
       <c r="AA38">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AB38">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="AC38">
-        <v>2.33</v>
+        <v>2.81</v>
       </c>
       <c r="AD38">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF38">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AG38">
-        <v>2.53</v>
+        <v>2.13</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6832,10 +6832,10 @@
         <v>3.25</v>
       </c>
       <c r="O40">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P40">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q40">
         <v>3.85</v>
@@ -6862,22 +6862,22 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA40">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB40">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC40">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
         <v>1.11</v>
@@ -8305,7 +8305,7 @@
         <v>5.5</v>
       </c>
       <c r="Q49">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="R49">
         <v>2.25</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK49">
         <v>2.33</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,55 +807,55 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3092,10 +3092,10 @@
         <v>3.43</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T17">
         <v>3</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O18">
         <v>3.9</v>
@@ -3297,7 +3297,7 @@
         <v>1.33</v>
       </c>
       <c r="AF18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG18">
         <v>2.93</v>
@@ -3316,7 +3316,7 @@
         <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>5.25</v>
       </c>
       <c r="P19">
-        <v>7.75</v>
+        <v>7.4</v>
       </c>
       <c r="Q19">
         <v>1.73</v>
@@ -3445,10 +3445,10 @@
         <v>5.75</v>
       </c>
       <c r="AA19">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AB19">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AC19">
         <v>2.11</v>
@@ -3925,7 +3925,7 @@
         <v>1.07</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.22</v>
@@ -3934,10 +3934,10 @@
         <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB22">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC22">
         <v>3.04</v>
@@ -3946,13 +3946,13 @@
         <v>1.29</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF22">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG22">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>3.2</v>
       </c>
       <c r="Q24">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="R24">
         <v>2.26</v>
@@ -4275,10 +4275,10 @@
         <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG24">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4577,7 +4577,7 @@
         <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y26">
         <v>1.17</v>
@@ -4586,25 +4586,25 @@
         <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AB26">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD26">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE26">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF26">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>1.49</v>
       </c>
       <c r="AB30">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="AC30">
         <v>2.23</v>
@@ -5250,13 +5250,13 @@
         <v>1.59</v>
       </c>
       <c r="AE30">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF30">
         <v>1.44</v>
       </c>
       <c r="AG30">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>4.8</v>
       </c>
       <c r="P31">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q31">
         <v>1.85</v>
@@ -5386,7 +5386,7 @@
         <v>2.14</v>
       </c>
       <c r="V31">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="W31">
         <v>1.18</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="O32">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="P32">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q32">
         <v>4.6</v>
@@ -5567,7 +5567,7 @@
         <v>1.36</v>
       </c>
       <c r="AB32">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="AC32">
         <v>1.86</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="O33">
         <v>4.1</v>
@@ -5697,7 +5697,7 @@
         <v>1.97</v>
       </c>
       <c r="Q33">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R33">
         <v>2.38</v>
@@ -5727,7 +5727,7 @@
         <v>6.23</v>
       </c>
       <c r="AA33">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AB33">
         <v>3</v>
@@ -5863,7 +5863,7 @@
         <v>3.62</v>
       </c>
       <c r="R34">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="S34">
         <v>1.22</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O35">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="P35">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="Q35">
         <v>2.3</v>
@@ -6195,7 +6195,7 @@
         <v>1.11</v>
       </c>
       <c r="T36">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="U36">
         <v>1.67</v>
@@ -6216,7 +6216,7 @@
         <v>9.5</v>
       </c>
       <c r="AA36">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AB36">
         <v>4.33</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P37">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q37">
-        <v>2.95</v>
+        <v>2.58</v>
       </c>
       <c r="R37">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T37">
-        <v>3.56</v>
+        <v>3.22</v>
       </c>
       <c r="U37">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="V37">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z37">
-        <v>4.7</v>
+        <v>3.82</v>
       </c>
       <c r="AA37">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AB37">
-        <v>2.33</v>
+        <v>2.01</v>
       </c>
       <c r="AC37">
-        <v>2.33</v>
+        <v>2.81</v>
       </c>
       <c r="AD37">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AF37">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.53</v>
+        <v>2.13</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q38">
-        <v>2.58</v>
+        <v>2.95</v>
       </c>
       <c r="R38">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S38">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.22</v>
+        <v>3.56</v>
       </c>
       <c r="U38">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z38">
-        <v>3.82</v>
+        <v>4.7</v>
       </c>
       <c r="AA38">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AB38">
-        <v>2.01</v>
+        <v>2.33</v>
       </c>
       <c r="AC38">
-        <v>2.81</v>
+        <v>2.33</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE38">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AF38">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AG38">
-        <v>2.13</v>
+        <v>2.53</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O40">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q40">
         <v>3.85</v>
@@ -6862,31 +6862,31 @@
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA40">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB40">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AC40">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE40">
         <v>1.11</v>
       </c>
       <c r="AF40">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG40">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -8305,10 +8305,10 @@
         <v>5.5</v>
       </c>
       <c r="Q49">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
         <v>1.3</v>
@@ -8338,7 +8338,7 @@
         <v>1.8</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC49">
         <v>2.83</v>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R3">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="O4">
         <v>3</v>
       </c>
       <c r="P4">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q4">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U4">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V4">
+        <v>1.33</v>
+      </c>
+      <c r="W4">
+        <v>1.06</v>
+      </c>
+      <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
+        <v>1.38</v>
+      </c>
+      <c r="Z4">
+        <v>2.62</v>
+      </c>
+      <c r="AA4">
+        <v>2.24</v>
+      </c>
+      <c r="AB4">
+        <v>1.55</v>
+      </c>
+      <c r="AC4">
+        <v>4.2</v>
+      </c>
+      <c r="AD4">
+        <v>1.16</v>
+      </c>
+      <c r="AE4">
+        <v>1.01</v>
+      </c>
+      <c r="AF4">
+        <v>1.95</v>
+      </c>
+      <c r="AG4">
+        <v>1.75</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.36</v>
       </c>
-      <c r="W4">
-        <v>1.07</v>
-      </c>
-      <c r="X4">
-        <v>1.02</v>
-      </c>
-      <c r="Y4">
-        <v>1.32</v>
-      </c>
-      <c r="Z4">
-        <v>2.88</v>
-      </c>
-      <c r="AA4">
-        <v>2.08</v>
-      </c>
-      <c r="AB4">
-        <v>1.64</v>
-      </c>
-      <c r="AC4">
-        <v>3.7</v>
-      </c>
-      <c r="AD4">
-        <v>1.2</v>
-      </c>
-      <c r="AE4">
-        <v>1.03</v>
-      </c>
-      <c r="AF4">
-        <v>1.85</v>
-      </c>
-      <c r="AG4">
-        <v>1.87</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.35</v>
-      </c>
       <c r="AK4">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
         <v>2.25</v>
@@ -1299,46 +1299,46 @@
         <v>3.6</v>
       </c>
       <c r="R6">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S6">
+        <v>1.36</v>
+      </c>
+      <c r="T6">
+        <v>2.9</v>
+      </c>
+      <c r="U6">
+        <v>2.75</v>
+      </c>
+      <c r="V6">
         <v>1.4</v>
       </c>
-      <c r="T6">
-        <v>2.8</v>
-      </c>
-      <c r="U6">
-        <v>2.81</v>
-      </c>
-      <c r="V6">
-        <v>1.34</v>
-      </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AB6">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AC6">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="AD6">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
         <v>1.75</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,65 +1450,65 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q7">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="R7">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.3</v>
+      </c>
+      <c r="Z7">
+        <v>2.97</v>
+      </c>
+      <c r="AA7">
+        <v>2.02</v>
+      </c>
+      <c r="AB7">
+        <v>1.68</v>
+      </c>
+      <c r="AC7">
+        <v>3.58</v>
+      </c>
+      <c r="AD7">
+        <v>1.21</v>
+      </c>
+      <c r="AE7">
         <v>1.03</v>
       </c>
-      <c r="Y7">
-        <v>1.38</v>
-      </c>
-      <c r="Z7">
-        <v>2.62</v>
-      </c>
-      <c r="AA7">
-        <v>2.24</v>
-      </c>
-      <c r="AB7">
-        <v>1.55</v>
-      </c>
-      <c r="AC7">
-        <v>4.2</v>
-      </c>
-      <c r="AD7">
-        <v>1.16</v>
-      </c>
-      <c r="AE7">
-        <v>1.01</v>
-      </c>
       <c r="AF7">
+        <v>1.75</v>
+      </c>
+      <c r="AG7">
         <v>1.95</v>
       </c>
-      <c r="AG7">
-        <v>1.75</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="T9">
-        <v>2.9</v>
+        <v>3.46</v>
       </c>
       <c r="U9">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="AA9">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AB9">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="O10">
         <v>3</v>
       </c>
       <c r="P10">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="Q10">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R10">
         <v>2.1</v>
@@ -1957,7 +1957,7 @@
         <v>1.4</v>
       </c>
       <c r="T10">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U10">
         <v>2.9</v>
@@ -1969,34 +1969,34 @@
         <v>1.07</v>
       </c>
       <c r="X10">
+        <v>1.02</v>
+      </c>
+      <c r="Y10">
+        <v>1.32</v>
+      </c>
+      <c r="Z10">
+        <v>2.88</v>
+      </c>
+      <c r="AA10">
+        <v>2.08</v>
+      </c>
+      <c r="AB10">
+        <v>1.64</v>
+      </c>
+      <c r="AC10">
+        <v>3.7</v>
+      </c>
+      <c r="AD10">
+        <v>1.2</v>
+      </c>
+      <c r="AE10">
         <v>1.03</v>
       </c>
-      <c r="Y10">
-        <v>1.33</v>
-      </c>
-      <c r="Z10">
-        <v>3.1</v>
-      </c>
-      <c r="AA10">
-        <v>2.04</v>
-      </c>
-      <c r="AB10">
-        <v>1.67</v>
-      </c>
-      <c r="AC10">
-        <v>3.5</v>
-      </c>
-      <c r="AD10">
-        <v>1.22</v>
-      </c>
-      <c r="AE10">
-        <v>1.04</v>
-      </c>
       <c r="AF10">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
+        <v>1.35</v>
+      </c>
+      <c r="AK10">
         <v>1.36</v>
-      </c>
-      <c r="AK10">
-        <v>1.55</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P17">
-        <v>1.91</v>
+        <v>2.82</v>
       </c>
       <c r="Q17">
-        <v>3.43</v>
+        <v>2.49</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S17">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="U17">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z17">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA17">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AB17">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="AC17">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="AD17">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AF17">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AG17">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
-        <v>2.49</v>
+        <v>3.43</v>
       </c>
       <c r="R18">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T18">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="V18">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA18">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB18">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="AC18">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="AD18">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AE18">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AG18">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AK18">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.84</v>
+        <v>2.43</v>
       </c>
       <c r="O20">
+        <v>3.12</v>
+      </c>
+      <c r="P20">
+        <v>2.87</v>
+      </c>
+      <c r="Q20">
         <v>3.08</v>
       </c>
-      <c r="P20">
-        <v>2.45</v>
-      </c>
-      <c r="Q20">
-        <v>3.7</v>
-      </c>
       <c r="R20">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S20">
         <v>1.4</v>
@@ -3599,31 +3599,31 @@
         <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z20">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AA20">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AB20">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AC20">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="AD20">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AG20">
         <v>1.83</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK20">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O21">
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q21">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R21">
         <v>2.1</v>
@@ -3759,19 +3759,19 @@
         <v>1.36</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
         <v>1.26</v>
       </c>
       <c r="Z21">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA21">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AB21">
         <v>1.82</v>
@@ -3805,7 +3805,7 @@
         <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q22">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.6</v>
+        <v>2.97</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W22">
         <v>1.07</v>
@@ -3928,31 +3928,31 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="AA22">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AB22">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AC22">
-        <v>3.04</v>
+        <v>3.51</v>
       </c>
       <c r="AD22">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE22">
         <v>1.06</v>
       </c>
       <c r="AF22">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AG22">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK22">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="Q23">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R23">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
         <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA23">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB23">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="AC23">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="AD23">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG23">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q24">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="R24">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.32</v>
+        <v>3.14</v>
       </c>
       <c r="U24">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V24">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z24">
-        <v>4.1</v>
+        <v>3.78</v>
       </c>
       <c r="AA24">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AB24">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="AC24">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="AD24">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,80 +4384,80 @@
         </is>
       </c>
       <c r="N25">
+        <v>2.37</v>
+      </c>
+      <c r="O25">
+        <v>3.4</v>
+      </c>
+      <c r="P25">
+        <v>2.9</v>
+      </c>
+      <c r="Q25">
+        <v>2.8</v>
+      </c>
+      <c r="R25">
         <v>2.2</v>
       </c>
-      <c r="O25">
-        <v>3.5</v>
-      </c>
-      <c r="P25">
-        <v>3.05</v>
-      </c>
-      <c r="Q25">
-        <v>2.7</v>
-      </c>
-      <c r="R25">
-        <v>2.16</v>
-      </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V25">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>3.78</v>
+        <v>3.66</v>
       </c>
       <c r="AA25">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AB25">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AC25">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AD25">
+        <v>1.28</v>
+      </c>
+      <c r="AE25">
+        <v>1.12</v>
+      </c>
+      <c r="AF25">
+        <v>1.7</v>
+      </c>
+      <c r="AG25">
+        <v>2.06</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
         <v>1.33</v>
       </c>
-      <c r="AE25">
-        <v>1.09</v>
-      </c>
-      <c r="AF25">
-        <v>1.61</v>
-      </c>
-      <c r="AG25">
-        <v>2.18</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.25</v>
-      </c>
       <c r="AK25">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O26">
         <v>3.6</v>
       </c>
       <c r="P26">
+        <v>2.2</v>
+      </c>
+      <c r="Q26">
+        <v>3.4</v>
+      </c>
+      <c r="R26">
         <v>2.3</v>
-      </c>
-      <c r="Q26">
-        <v>3.46</v>
-      </c>
-      <c r="R26">
-        <v>2.21</v>
       </c>
       <c r="S26">
         <v>1.28</v>
       </c>
       <c r="T26">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="U26">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W26">
         <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="AA26">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AC26">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD26">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE26">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
         <v>1.36</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q27">
         <v>3.5</v>
@@ -4725,13 +4725,13 @@
         <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
         <v>3.4</v>
       </c>
       <c r="U27">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="V27">
         <v>1.5</v>
@@ -4740,7 +4740,7 @@
         <v>1.12</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
         <v>1.15</v>
@@ -4749,13 +4749,13 @@
         <v>4.2</v>
       </c>
       <c r="AA27">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AB27">
         <v>2.23</v>
       </c>
       <c r="AC27">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="AD27">
         <v>1.45</v>
@@ -4764,7 +4764,7 @@
         <v>1.16</v>
       </c>
       <c r="AF27">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG27">
         <v>2.37</v>
@@ -4882,55 +4882,55 @@
         <v>3.86</v>
       </c>
       <c r="Q28">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T28">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="U28">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="V28">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W28">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z28">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AA28">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB28">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AC28">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="AD28">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AE28">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AG28">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="O32">
-        <v>4.65</v>
+        <v>4.1</v>
       </c>
       <c r="P32">
-        <v>1.52</v>
+        <v>1.97</v>
       </c>
       <c r="Q32">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="R32">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S32">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="U32">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="V32">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="W32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X32">
         <v>1</v>
       </c>
       <c r="Y32">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z32">
-        <v>7.5</v>
+        <v>6.23</v>
       </c>
       <c r="AA32">
+        <v>1.39</v>
+      </c>
+      <c r="AB32">
+        <v>3</v>
+      </c>
+      <c r="AC32">
+        <v>2.05</v>
+      </c>
+      <c r="AD32">
+        <v>1.81</v>
+      </c>
+      <c r="AE32">
+        <v>1.35</v>
+      </c>
+      <c r="AF32">
         <v>1.36</v>
       </c>
-      <c r="AB32">
-        <v>2.91</v>
-      </c>
-      <c r="AC32">
-        <v>1.86</v>
-      </c>
-      <c r="AD32">
-        <v>1.88</v>
-      </c>
-      <c r="AE32">
-        <v>1.39</v>
-      </c>
-      <c r="AF32">
-        <v>1.44</v>
-      </c>
       <c r="AG32">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AK32">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="O33">
-        <v>4.1</v>
+        <v>4.65</v>
       </c>
       <c r="P33">
-        <v>1.97</v>
+        <v>1.52</v>
       </c>
       <c r="Q33">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T33">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U33">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="V33">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="W33">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X33">
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z33">
-        <v>6.23</v>
+        <v>7.5</v>
       </c>
       <c r="AA33">
+        <v>1.36</v>
+      </c>
+      <c r="AB33">
+        <v>2.91</v>
+      </c>
+      <c r="AC33">
+        <v>1.86</v>
+      </c>
+      <c r="AD33">
+        <v>1.88</v>
+      </c>
+      <c r="AE33">
         <v>1.39</v>
       </c>
-      <c r="AB33">
-        <v>3</v>
-      </c>
-      <c r="AC33">
-        <v>2.05</v>
-      </c>
-      <c r="AD33">
-        <v>1.81</v>
-      </c>
-      <c r="AE33">
-        <v>1.35</v>
-      </c>
       <c r="AF33">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q37">
         <v>2.58</v>
@@ -6370,25 +6370,25 @@
         <v>1.08</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>3.82</v>
+        <v>3.45</v>
       </c>
       <c r="AA37">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB37">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AC37">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="AD37">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE37">
         <v>1.09</v>
@@ -6397,7 +6397,7 @@
         <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O38">
         <v>3.6</v>
       </c>
       <c r="P38">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q38">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="R38">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="U38">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="V38">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AA38">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AC38">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AD38">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AE38">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG38">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>

--- a/jogos_2026-11-03.xlsx
+++ b/jogos_2026-11-03.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Fujieda MYFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
+        <v>2.8</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>2.3</v>
+      </c>
+      <c r="Q6">
+        <v>3.5</v>
+      </c>
+      <c r="R6">
+        <v>2.1</v>
+      </c>
+      <c r="S6">
+        <v>1.4</v>
+      </c>
+      <c r="T6">
         <v>2.75</v>
       </c>
-      <c r="O6">
-        <v>3.2</v>
-      </c>
-      <c r="P6">
-        <v>2.25</v>
-      </c>
-      <c r="Q6">
-        <v>3.6</v>
-      </c>
-      <c r="R6">
-        <v>2.09</v>
-      </c>
-      <c r="S6">
+      <c r="U6">
+        <v>2.9</v>
+      </c>
+      <c r="V6">
         <v>1.36</v>
       </c>
-      <c r="T6">
-        <v>2.9</v>
-      </c>
-      <c r="U6">
-        <v>2.75</v>
-      </c>
-      <c r="V6">
-        <v>1.4</v>
-      </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA6">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AB6">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC6">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="AD6">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ventforet Kofu</t>
+          <t>Tegevajaro Miyazaki</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Tochigi City</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>3.46</v>
       </c>
       <c r="U7">
-        <v>2.81</v>
+        <v>2.23</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z7">
-        <v>2.97</v>
+        <v>4.45</v>
       </c>
       <c r="AA7">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>3.58</v>
+        <v>2.43</v>
       </c>
       <c r="AD7">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG7">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O8">
         <v>3</v>
       </c>
       <c r="P8">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T8">
-        <v>2.53</v>
+        <v>2.48</v>
       </c>
       <c r="U8">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z8">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AA8">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="AB8">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AC8">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD8">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE8">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG8">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.36</v>
       </c>
       <c r="AK8">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tegevajaro Miyazaki</t>
+          <t>Ventforet Kofu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tochigi City</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>3.46</v>
+        <v>2.8</v>
       </c>
       <c r="U9">
-        <v>2.23</v>
+        <v>2.81</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>4.45</v>
+        <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>1.57</v>
+        <v>2.02</v>
       </c>
       <c r="AB9">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AC9">
-        <v>2.43</v>
+        <v>3.58</v>
       </c>
       <c r="AD9">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK9">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fujieda MYFC</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
         <v>3</v>
       </c>
       <c r="P10">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="Q10">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="R10">
         <v>2.1</v>
@@ -1957,7 +1957,7 @@
         <v>1.4</v>
       </c>
       <c r="T10">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U10">
         <v>2.9</v>
@@ -1969,34 +1969,34 @@
         <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA10">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AB10">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD10">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.25</v>
+        <v>3.75</v>
       </c>
       <c r="O17">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
-        <v>2.49</v>
+        <v>3.43</v>
       </c>
       <c r="R17">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T17">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="U17">
-        <v>2.09</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
       <c r="Y17">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z17">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA17">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB17">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="AC17">
-        <v>2.08</v>
+        <v>2.56</v>
       </c>
       <c r="AD17">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AE17">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AG17">
-        <v>2.93</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AK17">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>1.91</v>
+        <v>2.82</v>
       </c>
       <c r="Q18">
-        <v>3.43</v>
+        <v>2.49</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="U18">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z18">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="AC18">
-        <v>2.56</v>
+        <v>2.08</v>
       </c>
       <c r="AD18">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AE18">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AF18">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AG18">
-        <v>2.3</v>
+        <v>2.93</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,49 +3569,49 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="O20">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="P20">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q20">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="R20">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="S20">
+        <v>1.36</v>
+      </c>
+      <c r="T20">
+        <v>2.9</v>
+      </c>
+      <c r="U20">
+        <v>2.75</v>
+      </c>
+      <c r="V20">
         <v>1.4</v>
       </c>
-      <c r="T20">
-        <v>2.62</v>
-      </c>
-      <c r="U20">
-        <v>3</v>
-      </c>
-      <c r="V20">
-        <v>1.33</v>
-      </c>
       <c r="W20">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AA20">
         <v>1.99</v>
       </c>
       <c r="AB20">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AC20">
         <v>3.42</v>
@@ -3620,13 +3620,13 @@
         <v>1.3</v>
       </c>
       <c r="AE20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG20">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O21">
         <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q21">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="S21">
         <v>1.36</v>
@@ -3753,43 +3753,43 @@
         <v>2.88</v>
       </c>
       <c r="U21">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V21">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z21">
-        <v>3</v>
+        <v>3.41</v>
       </c>
       <c r="AA21">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AB21">
         <v>1.82</v>
       </c>
       <c r="AC21">
-        <v>3.2</v>
+        <v>3.51</v>
       </c>
       <c r="AD21">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
         <v>1.06</v>
       </c>
       <c r="AF21">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AG21">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK21">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
+        <v>2.9</v>
+      </c>
+      <c r="Q22">
         <v>2.8</v>
       </c>
-      <c r="Q22">
-        <v>2.88</v>
-      </c>
       <c r="R22">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z22">
-        <v>3.41</v>
+        <v>3.66</v>
       </c>
       <c r="AA22">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AB22">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AC22">
-        <v>3.51</v>
+        <v>3.08</v>
       </c>
       <c r="AD22">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE22">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK22">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P23">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q23">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R23">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T23">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
         <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="AA23">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AB23">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AC23">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>2.2</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
         <v>3.05</v>
@@ -4251,7 +4251,7 @@
         <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
         <v>1.19</v>
@@ -4275,10 +4275,10 @@
         <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="Q25">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
+        <v>1.36</v>
+      </c>
+      <c r="T25">
+        <v>2.88</v>
+      </c>
+      <c r="U25">
+        <v>3</v>
+      </c>
+      <c r="V25">
         <v>1.33</v>
       </c>
-      <c r="T25">
-        <v>3</v>
-      </c>
-      <c r="U25">
-        <v>2.75</v>
-      </c>
-      <c r="V25">
-        <v>1.4</v>
-      </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
         <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>3.66</v>
+        <v>2.91</v>
       </c>
       <c r="AA25">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AB25">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC25">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AD25">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE25">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AG25">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O26">
         <v>3.6</v>
       </c>
       <c r="P26">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="R26">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S26">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T26">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U26">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
         <v>1.5</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="AA26">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AB26">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AC26">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="AD26">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG26">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         <v>3.25</v>
       </c>
       <c r="O27">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
         <v>2.05</v>
@@ -4722,52 +4722,52 @@
         <v>3.5</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T27">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U27">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V27">
         <v>1.5</v>
       </c>
       <c r="W27">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="AA27">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB27">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AC27">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="AD27">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -6868,7 +6868,7 @@
         <v>4.33</v>
       </c>
       <c r="AA40">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB40">
         <v>2.07</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hammam-Sousse</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Hammam-Sousse</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G44">
@@ -8305,10 +8305,10 @@
         <v>5.5</v>
       </c>
       <c r="Q49">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="R49">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S49">
         <v>1.3</v>
@@ -8332,7 +8332,7 @@
         <v>1.25</v>
       </c>
       <c r="Z49">
-        <v>3.58</v>
+        <v>4.04</v>
       </c>
       <c r="AA49">
         <v>1.8</v>
@@ -8347,7 +8347,7 @@
         <v>1.38</v>
       </c>
       <c r="AE49">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF49">
         <v>1.8</v>
